--- a/Figures/pairwise_adonis_22_same_sheet.xlsx
+++ b/Figures/pairwise_adonis_22_same_sheet.xlsx
@@ -416,7 +416,7 @@
         <v>2.06738655846647</v>
       </c>
       <c r="E6" t="n">
-        <v>0.117</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>3.84735391896983</v>
       </c>
       <c r="E12" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         <v>0.940385435103108</v>
       </c>
       <c r="E18" t="n">
-        <v>0.449</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="19">
